--- a/Сoaxial Сylinders v_1.11/Documents/Different/Оценка порядка точности.xlsx
+++ b/Сoaxial Сylinders v_1.11/Documents/Different/Оценка порядка точности.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Visual Studio\Coaxial Сylinders\Сoaxial Сylinders v_1.11\Сoaxial Сylinders v_1.11\Documents\Different\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561123CB-DB84-4FE8-B8C9-5DB902337D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F1A943-3532-4DB4-9D11-AEA7E230EBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5F365D3E-7A95-4138-9B28-2F5F42E608DA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{5F365D3E-7A95-4138-9B28-2F5F42E608DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Общее исследование (итог. табл)" sheetId="5" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Общее исследование (новая табл)" sheetId="6" r:id="rId3"/>
     <sheet name="Одна лопасть" sheetId="1" r:id="rId4"/>
     <sheet name="Без лопастей 2" sheetId="3" r:id="rId5"/>
+    <sheet name="Тест" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -130,8 +131,42 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Дмитрий</author>
+  </authors>
+  <commentList>
+    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{2D06495F-FE8C-4AEF-A10C-DE7AA8BA96DE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Дмитрий:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Количество ячеек сетки в данном столбце отличается от реальной сетки, так как модель в gmsh использовала не 13, а 91 точку на внешней границе</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="33">
   <si>
     <t>Ux</t>
   </si>
@@ -242,11 +277,53 @@
       <t>analytic</t>
     </r>
   </si>
+  <si>
+    <t>Ф_an</t>
+  </si>
+  <si>
+    <t>Ф_Integral_an</t>
+  </si>
+  <si>
+    <t>x: 0.0000</t>
+  </si>
+  <si>
+    <t>y: 0.2500</t>
+  </si>
+  <si>
+    <t>0.5195988279</t>
+  </si>
+  <si>
+    <t>Time: 4.0350</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0113755477 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0131018359 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0320966088 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0153158203 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.0003075375 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -0.0939867123 </t>
+  </si>
+  <si>
+    <t>0.1810062822</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="174" formatCode="0.000000000"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -763,7 +840,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -822,24 +899,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -858,8 +918,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -870,16 +945,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1206,29 +1284,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="42"/>
-      <c r="Q1" s="46" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="52"/>
+      <c r="Q1" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="48"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="43"/>
     </row>
     <row r="2" spans="1:20" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
@@ -1276,13 +1354,13 @@
       <c r="O2" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="49">
+      <c r="Q2" s="44">
         <f>AVERAGEA(M3:O8,K12:M17,K21:M26)</f>
         <v>1.1989367166624281</v>
       </c>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="51"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="46"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="26">
@@ -1505,7 +1583,7 @@
         <v>2.0777779862000001</v>
       </c>
       <c r="L7" s="54"/>
-      <c r="M7" s="56">
+      <c r="M7" s="40">
         <f t="shared" si="0"/>
         <v>1.7207935590298626</v>
       </c>
@@ -1547,30 +1625,30 @@
         <v>2.0858630634000002</v>
       </c>
       <c r="L8" s="55"/>
-      <c r="M8" s="57">
+      <c r="M8" s="47">
         <f>AVERAGE(M3:N7)</f>
         <v>1.8679448875568856</v>
       </c>
-      <c r="N8" s="58"/>
-      <c r="O8" s="59"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="49"/>
     </row>
     <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="45"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="58"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
@@ -1855,21 +1933,21 @@
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="45"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="58"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -2154,13 +2232,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A19:M19"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="Q2:T2"/>
     <mergeCell ref="M8:O8"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="L3:L8"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A19:M19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -2182,27 +2260,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="42"/>
-      <c r="O1" s="46" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="52"/>
+      <c r="O1" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="48"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="43"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
@@ -2244,13 +2322,13 @@
       <c r="M2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="49">
+      <c r="O2" s="44">
         <f>(K3+L3+M3+M4+L4+K4+K5+L5+L6+K6+K12+L12+M12+M13+L13+K13+K14+L14+L15+K15+K21+L21+M21+M22+L22+K22+K23+L23+L24+K24)/30</f>
         <v>0.91646730325433123</v>
       </c>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="51"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="46"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
@@ -2295,13 +2373,13 @@
         <f>LOG(ABS((J3-J5)/(J5-J7)),(A5/A3))</f>
         <v>0.93290176797265467</v>
       </c>
-      <c r="O3" s="52">
+      <c r="O3" s="59">
         <f>AVERAGEA(K3:M8,K12:M17,K21:M26)</f>
         <v>0.91646730325433123</v>
       </c>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
@@ -2525,21 +2603,21 @@
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="45"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="58"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
@@ -2864,21 +2942,21 @@
     </row>
     <row r="18" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="45"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="58"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -3231,29 +3309,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="42"/>
-      <c r="Q1" s="46" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="52"/>
+      <c r="Q1" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="48"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="43"/>
     </row>
     <row r="2" spans="1:20" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
@@ -3301,10 +3379,10 @@
       <c r="O2" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="51"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="46"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="26">
@@ -3353,10 +3431,10 @@
         <f>LOG(ABS((K3-K5)/(K5-K7)),(A5/A3))</f>
         <v>0.88206600284674996</v>
       </c>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
@@ -3562,23 +3640,23 @@
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="45"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="58"/>
     </row>
     <row r="10" spans="1:20" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34" t="s">
@@ -3835,23 +3913,23 @@
     </row>
     <row r="16" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="45"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="58"/>
     </row>
     <row r="18" spans="1:15" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34" t="s">
@@ -4134,21 +4212,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="45"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="58"/>
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -4438,21 +4516,21 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="42"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="52"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
@@ -5031,4 +5109,1189 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCABF4D-EFA4-4BEF-BBE3-4DBFB37F1A27}">
+  <dimension ref="A1:U32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="52"/>
+      <c r="Q1" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="43"/>
+    </row>
+    <row r="2" spans="1:21" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="44">
+        <f>AVERAGEA(M3:O8,K12:M17,K21:M26)</f>
+        <v>1.2125041478595024</v>
+      </c>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="46"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="26">
+        <v>872</v>
+      </c>
+      <c r="B3" s="4">
+        <v>4.7154514299999999E-2</v>
+      </c>
+      <c r="C3" s="4">
+        <v>5.3522793800000003E-2</v>
+      </c>
+      <c r="D3" s="4">
+        <v>6.166787E-2</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.13141868540000001</v>
+      </c>
+      <c r="F3" s="4">
+        <v>6.4092994E-2</v>
+      </c>
+      <c r="G3" s="4">
+        <v>5.3941960000000004E-3</v>
+      </c>
+      <c r="H3" s="4">
+        <v>-0.1059270937</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1.2059736935000001</v>
+      </c>
+      <c r="J3" s="27">
+        <v>5.5535868129999999</v>
+      </c>
+      <c r="K3" s="23">
+        <v>0.45752339489999999</v>
+      </c>
+      <c r="L3" s="53">
+        <f>2*3.14159265358979/3/4</f>
+        <v>0.52359877559829837</v>
+      </c>
+      <c r="M3" s="29">
+        <f>ABS(LN(ABS(($L$3-K3)/($L$3-K4))/LN(B3/B4)))</f>
+        <v>1.6537149334933148</v>
+      </c>
+      <c r="N3" s="30">
+        <f>(LOG(ABS((L3-K4)/K4),2)-LOG(ABS((L3-K3)/K3),2))/(LOG((D4),2) - LOG(D3,2))</f>
+        <v>1.9766424218009115</v>
+      </c>
+      <c r="O3" s="31">
+        <f>LOG(ABS((K3-K5)/(K5-K7)),(A5/A3))</f>
+        <v>0.87471592258430197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>1758</v>
+      </c>
+      <c r="B4" s="2">
+        <v>3.26496301E-2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3.7391840699999998E-2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4.2843740700000001E-2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8.6065754800000005E-2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4.4363140299999999E-2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2.5992445999999999E-3</v>
+      </c>
+      <c r="H4" s="2">
+        <v>-9.8004582600000001E-2</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2.2780368650999998</v>
+      </c>
+      <c r="J4" s="12">
+        <v>9.2772045229</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.4892058306</v>
+      </c>
+      <c r="L4" s="54"/>
+      <c r="M4" s="29">
+        <f t="shared" ref="M4:M7" si="0">ABS(LN(ABS(($L$3-K4)/($L$3-K5))/LN(B4/B5)))</f>
+        <v>1.672140493312158</v>
+      </c>
+      <c r="N4" s="30">
+        <f>(LOG(ABS((L3-K5)/K5),2)-LOG(ABS((L3-K4)/K4),2))/(LOG((D5),2) - LOG(D4,2))</f>
+        <v>1.8904788327842799</v>
+      </c>
+      <c r="O4" s="19"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>3500</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2.2892365800000002E-2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2.62874931E-2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3.0072090400000001E-2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>6.0546886500000001E-2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>3.0602556199999999E-2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1.2338153E-3</v>
+      </c>
+      <c r="H5" s="2">
+        <v>-9.5210931100000007E-2</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1.7024157568</v>
+      </c>
+      <c r="J5" s="12">
+        <v>6.4731611223999996</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0.50540164669999998</v>
+      </c>
+      <c r="L5" s="54"/>
+      <c r="M5" s="29">
+        <f t="shared" si="0"/>
+        <v>1.856549429848275</v>
+      </c>
+      <c r="N5" s="30">
+        <f>(LOG(ABS((L3-K6)/K6),2)-LOG(ABS((L3-K5)/K5),2))/(LOG((D6),2) - LOG(D5,2))</f>
+        <v>2.3617100112868386</v>
+      </c>
+      <c r="O5" s="19"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>6922</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1.6157448299999998E-2</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1.8571305199999999E-2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2.12338465E-2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4.34101873E-2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2.1752620100000002E-2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>6.1713019999999998E-4</v>
+      </c>
+      <c r="H6" s="2">
+        <v>-9.4447774700000001E-2</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1.8924469414</v>
+      </c>
+      <c r="J6" s="12">
+        <v>7.5691573292000003</v>
+      </c>
+      <c r="K6" s="60">
+        <v>0.51544032480000002</v>
+      </c>
+      <c r="L6" s="54"/>
+      <c r="M6" s="29">
+        <f t="shared" si="0"/>
+        <v>1.7599841902693683</v>
+      </c>
+      <c r="N6" s="30">
+        <f>(LOG(ABS((L3-K7)/K7),2)-LOG(ABS((L3-K6)/K6),2))/(LOG((D7),2) - LOG(D6,2))</f>
+        <v>2.0577229406257889</v>
+      </c>
+      <c r="O6" s="19"/>
+    </row>
+    <row r="7" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="35">
+        <v>13810</v>
+      </c>
+      <c r="B7" s="36">
+        <v>1.13755477E-2</v>
+      </c>
+      <c r="C7" s="36">
+        <v>1.3101835900000001E-2</v>
+      </c>
+      <c r="D7" s="36">
+        <v>1.4958836499999999E-2</v>
+      </c>
+      <c r="E7" s="36">
+        <v>3.2096608800000002E-2</v>
+      </c>
+      <c r="F7" s="36">
+        <v>1.53158203E-2</v>
+      </c>
+      <c r="G7" s="36">
+        <v>3.0753749999999999E-4</v>
+      </c>
+      <c r="H7" s="36">
+        <v>-9.3986712299999997E-2</v>
+      </c>
+      <c r="I7" s="36">
+        <v>1.8896757569</v>
+      </c>
+      <c r="J7" s="37">
+        <v>7.6478939668999999</v>
+      </c>
+      <c r="K7" s="36">
+        <v>0.5195988279</v>
+      </c>
+      <c r="L7" s="54"/>
+      <c r="M7" s="40">
+        <f t="shared" si="0"/>
+        <v>1.9677071372256139</v>
+      </c>
+      <c r="N7" s="38"/>
+      <c r="O7" s="39"/>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>27514</v>
+      </c>
+      <c r="B8" s="9">
+        <v>8.0284467000000005E-3</v>
+      </c>
+      <c r="C8" s="9">
+        <v>9.2536120999999992E-3</v>
+      </c>
+      <c r="D8" s="9">
+        <v>1.0560271600000001E-2</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2.21376213E-2</v>
+      </c>
+      <c r="F8" s="9">
+        <v>1.1496776300000001E-2</v>
+      </c>
+      <c r="G8" s="9">
+        <v>1.724056E-4</v>
+      </c>
+      <c r="H8" s="9">
+        <v>-9.2917982900000001E-2</v>
+      </c>
+      <c r="I8" s="9">
+        <v>1.7331657727000001</v>
+      </c>
+      <c r="J8" s="9">
+        <v>7.0100717196</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0.5219943548</v>
+      </c>
+      <c r="L8" s="55"/>
+      <c r="M8" s="47">
+        <f>AVERAGE(M3:N7)</f>
+        <v>1.9107389322940607</v>
+      </c>
+      <c r="N8" s="48"/>
+      <c r="O8" s="49"/>
+      <c r="Q8" s="23">
+        <v>1.8295565998000001</v>
+      </c>
+      <c r="R8">
+        <f>Q8/K3</f>
+        <v>3.9988263336782652</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q9" s="2">
+        <v>1.9565688275999999</v>
+      </c>
+      <c r="R9">
+        <f t="shared" ref="R9:R13" si="1">Q9/K4</f>
+        <v>3.9994797797080874</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="58"/>
+      <c r="Q10" s="2">
+        <v>2.0214536595000001</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>3.9996974143218598</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>2.0615488725</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>3.9995878733390087</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>437</v>
+      </c>
+      <c r="B12" s="2">
+        <v>6.8541834900000001E-2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>7.7674038000000001E-2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>8.9621687699999994E-2</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.17767096639999999</v>
+      </c>
+      <c r="F12" s="2">
+        <v>9.4158790899999997E-2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1.16163325E-2</v>
+      </c>
+      <c r="H12" s="2">
+        <v>-0.59209408549999998</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1.7889844999999999E-3</v>
+      </c>
+      <c r="J12" s="12">
+        <v>4.8251834757000003</v>
+      </c>
+      <c r="K12" s="17">
+        <f>ABS(LOG(ABS((J12-J13)/(J13-J14)),(A13/A12)))</f>
+        <v>1.4531371704126101</v>
+      </c>
+      <c r="L12" s="18">
+        <f>ABS((LOG(ABS((J13-J14)/J14),2)-LOG(ABS((J12-J13)/J13),2))/(LOG((D14),2) - LOG(D12,2)))</f>
+        <v>1.2105805487661288</v>
+      </c>
+      <c r="M12" s="19">
+        <f>LOG(ABS((J12-J14)/(J14-J16)),(A14/A12))</f>
+        <v>0.5799037599141148</v>
+      </c>
+      <c r="Q12" s="36">
+        <v>2.0777779862000001</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>3.9988119191829301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <v>859</v>
+      </c>
+      <c r="B13" s="2">
+        <v>4.7630490800000001E-2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>5.4193011399999998E-2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>6.2338799E-2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.13672689590000001</v>
+      </c>
+      <c r="F13" s="2">
+        <v>6.6807384600000005E-2</v>
+      </c>
+      <c r="G13" s="2">
+        <v>5.8127980999999997E-3</v>
+      </c>
+      <c r="H13" s="2">
+        <v>-0.58272351310000003</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1.6649465E-3</v>
+      </c>
+      <c r="J13" s="12">
+        <v>4.9779540988999997</v>
+      </c>
+      <c r="K13" s="17">
+        <f t="shared" ref="K13:K15" si="2">ABS(LOG(ABS((J13-J14)/(J14-J15)),(A14/A13)))</f>
+        <v>1.2842981265676239</v>
+      </c>
+      <c r="L13" s="18">
+        <f t="shared" ref="L13:L15" si="3">(LOG(ABS((J14-J15)/J15),2)-LOG(ABS((J13-J14)/J14),2))/(LOG((D15),2) - LOG(D13,2))</f>
+        <v>1.3066299597737223</v>
+      </c>
+      <c r="M13" s="19">
+        <f>LOG(ABS((J13-J15)/(J15-J17)),(A15/A13))</f>
+        <v>0.95189348394685913</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>2.0858630634000002</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="1"/>
+        <v>3.9959494661569472</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>1779</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3.2393254900000001E-2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3.7021824799999999E-2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>4.2495812500000001E-2</v>
+      </c>
+      <c r="E14" s="2">
+        <v>8.7485034099999998E-2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>4.4023539700000003E-2</v>
+      </c>
+      <c r="G14" s="2">
+        <v>2.5723743000000002E-3</v>
+      </c>
+      <c r="H14" s="2">
+        <v>-0.52223565679999995</v>
+      </c>
+      <c r="I14" s="2">
+        <v>3.3421199999999998E-5</v>
+      </c>
+      <c r="J14" s="12">
+        <v>5.3858531082000001</v>
+      </c>
+      <c r="K14" s="17">
+        <f t="shared" si="2"/>
+        <v>0.86894459015045133</v>
+      </c>
+      <c r="L14" s="18">
+        <f t="shared" si="3"/>
+        <v>0.87443373771738742</v>
+      </c>
+      <c r="M14" s="19"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>3531</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2.2701051699999999E-2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>2.59997805E-2</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2.98017226E-2</v>
+      </c>
+      <c r="E15" s="2">
+        <v>6.2895145E-2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3.1715278700000002E-2</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1.3205432E-3</v>
+      </c>
+      <c r="H15" s="2">
+        <v>-0.52052446190000001</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.9280999999999995E-6</v>
+      </c>
+      <c r="J15" s="12">
+        <v>5.5459856852999998</v>
+      </c>
+      <c r="K15" s="17">
+        <f t="shared" si="2"/>
+        <v>0.58200197308156687</v>
+      </c>
+      <c r="L15" s="18">
+        <f t="shared" si="3"/>
+        <v>0.56933926308422622</v>
+      </c>
+      <c r="M15" s="19"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>6923</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.6073853799999999E-2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1.8459330999999999E-2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2.1117931400000001E-2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4.4421197000000003E-2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2.2025218900000001E-2</v>
+      </c>
+      <c r="G16" s="2">
+        <v>6.3842550000000004E-4</v>
+      </c>
+      <c r="H16" s="2">
+        <v>-0.51826271589999995</v>
+      </c>
+      <c r="I16" s="2">
+        <v>2.5502000000000002E-6</v>
+      </c>
+      <c r="J16" s="12">
+        <v>5.6342481339999999</v>
+      </c>
+      <c r="K16" s="17"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="19"/>
+      <c r="Q16">
+        <v>4.8325820840000002</v>
+      </c>
+      <c r="R16">
+        <f>Q16/I3</f>
+        <v>4.0072035650916957</v>
+      </c>
+      <c r="T16" s="4">
+        <v>1.2059736935000001</v>
+      </c>
+      <c r="U16" s="27">
+        <f>J3/4</f>
+        <v>1.38839670325</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>14113</v>
+      </c>
+      <c r="B17" s="9">
+        <v>1.1184787700000001E-2</v>
+      </c>
+      <c r="C17" s="9">
+        <v>1.2852364599999999E-2</v>
+      </c>
+      <c r="D17" s="9">
+        <v>1.4699695400000001E-2</v>
+      </c>
+      <c r="E17" s="9">
+        <v>3.06687538E-2</v>
+      </c>
+      <c r="F17" s="9">
+        <v>1.55467682E-2</v>
+      </c>
+      <c r="G17" s="9">
+        <v>3.1684209999999999E-4</v>
+      </c>
+      <c r="H17" s="9">
+        <v>-0.50637611400000004</v>
+      </c>
+      <c r="I17" s="9">
+        <v>1.4286E-6</v>
+      </c>
+      <c r="J17" s="13">
+        <v>5.6938967766999999</v>
+      </c>
+      <c r="K17" s="20"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="22"/>
+      <c r="Q17">
+        <v>9.1256722890000006</v>
+      </c>
+      <c r="R17">
+        <f>Q17/I4</f>
+        <v>4.0059370543151447</v>
+      </c>
+      <c r="T17" s="2">
+        <v>2.2780368650999998</v>
+      </c>
+      <c r="U17" s="27">
+        <f t="shared" ref="U17:U21" si="4">J4/4</f>
+        <v>2.319301130725</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q18">
+        <v>6.8370392359999999</v>
+      </c>
+      <c r="R18">
+        <f t="shared" ref="R17:R21" si="5">Q18/I5</f>
+        <v>4.0160808008799558</v>
+      </c>
+      <c r="T18" s="2">
+        <v>1.7024157568</v>
+      </c>
+      <c r="U18" s="27">
+        <f t="shared" si="4"/>
+        <v>1.6182902805999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="58"/>
+      <c r="Q19">
+        <v>7.6196655719999997</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="5"/>
+        <v>4.0263562508986919</v>
+      </c>
+      <c r="T19" s="2">
+        <v>1.8924469414</v>
+      </c>
+      <c r="U19" s="27">
+        <f t="shared" si="4"/>
+        <v>1.8922893323000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q20">
+        <v>7.6611216930000001</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="5"/>
+        <v>4.0541990682930793</v>
+      </c>
+      <c r="T20" s="36">
+        <v>1.8896757569</v>
+      </c>
+      <c r="U20" s="27">
+        <f>J7/4</f>
+        <v>1.911973491725</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <v>437</v>
+      </c>
+      <c r="B21" s="2">
+        <v>6.9058050300000007E-2</v>
+      </c>
+      <c r="C21" s="2">
+        <v>7.7832715400000002E-2</v>
+      </c>
+      <c r="D21" s="2">
+        <v>9.0160010400000004E-2</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.19779184520000001</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.1011968687</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1.3352957699999999E-2</v>
+      </c>
+      <c r="H21" s="2">
+        <v>-8.4039826999999998E-3</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1.1551E-5</v>
+      </c>
+      <c r="J21" s="12">
+        <v>6.1697157708999999</v>
+      </c>
+      <c r="K21" s="17">
+        <f>ABS(LOG(ABS((J21-J22)/(J22-J23)),(A22/A21)))</f>
+        <v>0.91250133049327231</v>
+      </c>
+      <c r="L21" s="18">
+        <f>ABS((LOG(ABS((J22-J23)/J23),2)-LOG(ABS((J21-J22)/J22),2))/(LOG((D23),2) - LOG(D21,2)))</f>
+        <v>0.76131205297079252</v>
+      </c>
+      <c r="M21" s="19">
+        <f>LOG(ABS((J21-J23)/(J23-J25)),(A23/A21))</f>
+        <v>0.5567045284524712</v>
+      </c>
+      <c r="Q21">
+        <v>7.1106344769999996</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="5"/>
+        <v>4.1026857263184633</v>
+      </c>
+      <c r="T21" s="9">
+        <v>1.7331325641999999</v>
+      </c>
+      <c r="U21" s="27">
+        <f>J8/4</f>
+        <v>1.7525179299</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>869</v>
+      </c>
+      <c r="B22" s="2">
+        <v>4.73522096E-2</v>
+      </c>
+      <c r="C22" s="2">
+        <v>5.3748878799999997E-2</v>
+      </c>
+      <c r="D22" s="2">
+        <v>6.1916103600000001E-2</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.1351808699</v>
+      </c>
+      <c r="F22" s="2">
+        <v>7.0694914499999997E-2</v>
+      </c>
+      <c r="G22" s="2">
+        <v>6.5809014999999998E-3</v>
+      </c>
+      <c r="H22" s="2">
+        <v>-6.3051330999999997E-3</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1.3873E-6</v>
+      </c>
+      <c r="J22" s="12">
+        <v>6.3710281466999996</v>
+      </c>
+      <c r="K22" s="17">
+        <f t="shared" ref="K22:K24" si="6">ABS(LOG(ABS((J22-J23)/(J23-J24)),(A23/A22)))</f>
+        <v>1.1406334425098277</v>
+      </c>
+      <c r="L22" s="18">
+        <f t="shared" ref="L22:L24" si="7">(LOG(ABS((J23-J24)/J24),2)-LOG(ABS((J22-J23)/J23),2))/(LOG((D24),2) - LOG(D22,2))</f>
+        <v>1.1326024907847352</v>
+      </c>
+      <c r="M22" s="19">
+        <f>LOG(ABS((J22-J24)/(J24-J26)),(A26/A24))</f>
+        <v>0.85610450062744414</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>1757</v>
+      </c>
+      <c r="B23" s="2">
+        <v>3.2494560499999998E-2</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3.7098392299999998E-2</v>
+      </c>
+      <c r="D23" s="2">
+        <v>4.2655983000000001E-2</v>
+      </c>
+      <c r="E23" s="2">
+        <v>8.7426870599999998E-2</v>
+      </c>
+      <c r="F23" s="2">
+        <v>4.5782799399999997E-2</v>
+      </c>
+      <c r="G23" s="2">
+        <v>2.7453102E-3</v>
+      </c>
+      <c r="H23" s="2">
+        <v>-5.1650263000000002E-3</v>
+      </c>
+      <c r="I23" s="2">
+        <v>2.586E-7</v>
+      </c>
+      <c r="J23" s="12">
+        <v>6.7479810618</v>
+      </c>
+      <c r="K23" s="17">
+        <f t="shared" si="6"/>
+        <v>0.79576595691417062</v>
+      </c>
+      <c r="L23" s="18">
+        <f t="shared" si="7"/>
+        <v>0.79413089970729278</v>
+      </c>
+      <c r="M23" s="19"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>3497</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2.2707022300000001E-2</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2.5972650900000002E-2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2.9813035500000001E-2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>6.5650928600000005E-2</v>
+      </c>
+      <c r="F24" s="2">
+        <v>3.2343383699999999E-2</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1.3637406E-3</v>
+      </c>
+      <c r="H24" s="2">
+        <v>-5.6489306999999997E-3</v>
+      </c>
+      <c r="I24" s="2">
+        <v>3.39E-7</v>
+      </c>
+      <c r="J24" s="12">
+        <v>6.9168447097000003</v>
+      </c>
+      <c r="K24" s="17">
+        <f t="shared" si="6"/>
+        <v>0.48887199952270982</v>
+      </c>
+      <c r="L24" s="18">
+        <f t="shared" si="7"/>
+        <v>0.48573352272225856</v>
+      </c>
+      <c r="M24" s="19"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>6907</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1.6002791299999999E-2</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1.8365861599999998E-2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2.1026843600000001E-2</v>
+      </c>
+      <c r="E25" s="2">
+        <v>4.4822349800000001E-2</v>
+      </c>
+      <c r="F25" s="2">
+        <v>2.2907505500000001E-2</v>
+      </c>
+      <c r="G25" s="2">
+        <v>6.8269550000000004E-4</v>
+      </c>
+      <c r="H25" s="2">
+        <v>-4.7245211000000002E-3</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1.3399999999999999E-8</v>
+      </c>
+      <c r="J25" s="12">
+        <v>7.0144925689999997</v>
+      </c>
+      <c r="K25" s="17"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="19"/>
+    </row>
+    <row r="26" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>13883</v>
+      </c>
+      <c r="B26" s="9">
+        <v>1.1201387199999999E-2</v>
+      </c>
+      <c r="C26" s="9">
+        <v>1.28763743E-2</v>
+      </c>
+      <c r="D26" s="9">
+        <v>1.47239042E-2</v>
+      </c>
+      <c r="E26" s="9">
+        <v>3.03175054E-2</v>
+      </c>
+      <c r="F26" s="9">
+        <v>1.5621945599999999E-2</v>
+      </c>
+      <c r="G26" s="9">
+        <v>3.2000030000000002E-4</v>
+      </c>
+      <c r="H26" s="9">
+        <v>-2.9596262E-3</v>
+      </c>
+      <c r="I26" s="9">
+        <v>4.3999999999999997E-9</v>
+      </c>
+      <c r="J26" s="13">
+        <v>7.0845017800000001</v>
+      </c>
+      <c r="K26" s="20"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="22"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" t="s">
+        <v>0</v>
+      </c>
+      <c r="I31" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" t="s">
+        <v>8</v>
+      </c>
+      <c r="L31" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" t="s">
+        <v>25</v>
+      </c>
+      <c r="P31" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>13810</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32">
+        <v>1.4958836499999999E-2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H32" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32">
+        <v>1.8896757569</v>
+      </c>
+      <c r="J32" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="L3:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="A10:M10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>